--- a/Vaulta_AUM_Model_v1.xlsx
+++ b/Vaulta_AUM_Model_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Vaulta-AUM-Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20874963-FDC6-4573-AADD-9E36A0EA4F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1D8903-C1E6-468F-B5D7-D5981D55022B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="323">
   <si>
     <t xml:space="preserve">  VAULTA — AUM MODEL v1</t>
   </si>
@@ -583,6 +583,12 @@
   </si>
   <si>
     <t>TOTAL WALLET BALANCES (avg)</t>
+  </si>
+  <si>
+    <t>TOTAL WALLET BALANCES (end of period)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Revenue uses the AVERAGE balance (income accrues over the quarter). The crossover ratio uses the END-OF-PERIOD balance, because it compares two stocks.</t>
   </si>
   <si>
     <t xml:space="preserve">  ACTIVE CONSUMERS BY SEGMENT (end of period)</t>
@@ -1628,7 +1634,7 @@
       </c>
       <c r="C10" s="10">
         <f>'Crossover Analysis'!$G$13</f>
-        <v>0.43395631898483283</v>
+        <v>0.39943431599793822</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -1637,7 +1643,7 @@
       </c>
       <c r="C11" s="11">
         <f>'Crossover Analysis'!$G$15</f>
-        <v>4.4244084392906506</v>
+        <v>4.8067978215720224</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -1861,23 +1867,23 @@
       </c>
       <c r="C23" s="16">
         <f>'Revenue Comparison'!$C$40</f>
-        <v>14764125.523048799</v>
+        <v>18900000</v>
       </c>
       <c r="D23" s="16">
         <f>'Revenue Comparison'!$D$40</f>
-        <v>64640745.986803554</v>
+        <v>74681250</v>
       </c>
       <c r="E23" s="16">
         <f>'Revenue Comparison'!$E$40</f>
-        <v>210308962.43938738</v>
+        <v>237750000</v>
       </c>
       <c r="F23" s="16">
         <f>'Revenue Comparison'!$F$40</f>
-        <v>533532019.70545787</v>
+        <v>594375000</v>
       </c>
       <c r="G23" s="16">
         <f>'Revenue Comparison'!$G$40</f>
-        <v>1094182806.8164268</v>
+        <v>1188750000</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -2869,7 +2875,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3966,706 +3972,796 @@
         <v>1094182806.8164268</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B20" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B22" s="9" t="s">
+      <c r="C20" s="15">
+        <f t="shared" ref="C20:V20" si="5">C12*C18</f>
+        <v>3360948.0849735644</v>
+      </c>
+      <c r="D20" s="15">
+        <f t="shared" si="5"/>
+        <v>5976704.7777182376</v>
+      </c>
+      <c r="E20" s="15">
+        <f t="shared" si="5"/>
+        <v>10628251.046097599</v>
+      </c>
+      <c r="F20" s="15">
+        <f t="shared" si="5"/>
+        <v>18900000</v>
+      </c>
+      <c r="G20" s="15">
+        <f t="shared" si="5"/>
+        <v>29185056.957170233</v>
+      </c>
+      <c r="H20" s="15">
+        <f t="shared" si="5"/>
+        <v>39918807.245144486</v>
+      </c>
+      <c r="I20" s="15">
+        <f t="shared" si="5"/>
+        <v>54600241.973607101</v>
+      </c>
+      <c r="J20" s="15">
+        <f t="shared" si="5"/>
+        <v>74681250</v>
+      </c>
+      <c r="K20" s="15">
+        <f t="shared" si="5"/>
+        <v>108186123.33526988</v>
+      </c>
+      <c r="L20" s="15">
+        <f t="shared" si="5"/>
+        <v>140654796.84319338</v>
+      </c>
+      <c r="M20" s="15">
+        <f t="shared" si="5"/>
+        <v>182867924.87877479</v>
+      </c>
+      <c r="N20" s="15">
+        <f t="shared" si="5"/>
+        <v>237750000</v>
+      </c>
+      <c r="O20" s="15">
+        <f t="shared" si="5"/>
+        <v>298954797.9071179</v>
+      </c>
+      <c r="P20" s="15">
+        <f t="shared" si="5"/>
+        <v>375915756.85251611</v>
+      </c>
+      <c r="Q20" s="15">
+        <f t="shared" si="5"/>
+        <v>472689039.41091573</v>
+      </c>
+      <c r="R20" s="15">
+        <f t="shared" si="5"/>
+        <v>594375000</v>
+      </c>
+      <c r="S20" s="15">
+        <f t="shared" si="5"/>
+        <v>706834978.97974229</v>
+      </c>
+      <c r="T20" s="15">
+        <f t="shared" si="5"/>
+        <v>840573186.13550842</v>
+      </c>
+      <c r="U20" s="15">
+        <f t="shared" si="5"/>
+        <v>999615613.63285315</v>
+      </c>
+      <c r="V20" s="15">
+        <f t="shared" si="5"/>
+        <v>1188750000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B24" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="C22" s="40">
+      <c r="C24" s="40">
         <f>C12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!C$6)</f>
         <v>1066.9676460233538</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D24" s="40">
         <f>D12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!D$6)</f>
         <v>1897.3665961010277</v>
       </c>
-      <c r="E22" s="40">
+      <c r="E24" s="40">
         <f>E12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!E$6)</f>
         <v>3374.0479511420949</v>
       </c>
-      <c r="F22" s="40">
+      <c r="F24" s="40">
         <f>F12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!F$6)</f>
         <v>6000</v>
       </c>
-      <c r="G22" s="40">
+      <c r="G24" s="40">
         <f>G12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!G$6)</f>
         <v>6496.9663993700578</v>
       </c>
-      <c r="H22" s="40">
+      <c r="H24" s="40">
         <f>H12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!H$6)</f>
         <v>8886.436293588109</v>
       </c>
-      <c r="I22" s="40">
+      <c r="I24" s="40">
         <f>I12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!I$6)</f>
         <v>12154.711159912535</v>
       </c>
-      <c r="J22" s="40">
+      <c r="J24" s="40">
         <f>J12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!J$6)</f>
         <v>16625</v>
       </c>
-      <c r="K22" s="40">
+      <c r="K24" s="40">
         <f>K12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!K$6)</f>
         <v>15926.453487842044</v>
       </c>
-      <c r="L22" s="40">
+      <c r="L24" s="40">
         <f>L12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!L$6)</f>
         <v>20706.279240848657</v>
       </c>
-      <c r="M22" s="40">
+      <c r="M24" s="40">
         <f>M12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!M$6)</f>
         <v>26920.61985597105</v>
       </c>
-      <c r="N22" s="40">
+      <c r="N24" s="40">
         <f>N12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!N$6)</f>
         <v>35000</v>
       </c>
-      <c r="O22" s="40">
+      <c r="O24" s="40">
         <f>O12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!O$6)</f>
         <v>44010.170038902739</v>
       </c>
-      <c r="P22" s="40">
+      <c r="P24" s="40">
         <f>P12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!P$6)</f>
         <v>55339.859052946638</v>
       </c>
-      <c r="Q22" s="40">
+      <c r="Q24" s="40">
         <f>Q12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!Q$6)</f>
         <v>69586.188767116924</v>
       </c>
-      <c r="R22" s="40">
+      <c r="R24" s="40">
         <f>R12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!R$6)</f>
         <v>87500</v>
       </c>
-      <c r="S22" s="40">
+      <c r="S24" s="40">
         <f>S12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!S$6)</f>
         <v>104055.62256273809</v>
       </c>
-      <c r="T22" s="40">
+      <c r="T24" s="40">
         <f>T12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!T$6)</f>
         <v>123743.68670764581</v>
       </c>
-      <c r="U22" s="40">
+      <c r="U24" s="40">
         <f>U12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!U$6)</f>
         <v>147156.87266940004</v>
       </c>
-      <c r="V22" s="40">
+      <c r="V24" s="40">
         <f>V12*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!V$6)</f>
         <v>175000</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B23" s="9" t="s">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B25" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="40">
+      <c r="C25" s="40">
         <f>C12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!C$6)</f>
         <v>533.48382301167692</v>
       </c>
-      <c r="D23" s="40">
+      <c r="D25" s="40">
         <f>D12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!D$6)</f>
         <v>948.68329805051383</v>
       </c>
-      <c r="E23" s="40">
+      <c r="E25" s="40">
         <f>E12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!E$6)</f>
         <v>1687.0239755710475</v>
       </c>
-      <c r="F23" s="40">
+      <c r="F25" s="40">
         <f>F12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!F$6)</f>
         <v>3000</v>
       </c>
-      <c r="G23" s="40">
+      <c r="G25" s="40">
         <f>G12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!G$6)</f>
         <v>5129.1839995026776</v>
       </c>
-      <c r="H23" s="40">
+      <c r="H25" s="40">
         <f>H12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!H$6)</f>
         <v>7015.6076002011396</v>
       </c>
-      <c r="I23" s="40">
+      <c r="I25" s="40">
         <f>I12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!I$6)</f>
         <v>9595.8245999309493</v>
       </c>
-      <c r="J23" s="40">
+      <c r="J25" s="40">
         <f>J12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!J$6)</f>
         <v>13125</v>
       </c>
-      <c r="K23" s="40">
+      <c r="K25" s="40">
         <f>K12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!K$6)</f>
         <v>20476.86877008263</v>
       </c>
-      <c r="L23" s="40">
+      <c r="L25" s="40">
         <f>L12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!L$6)</f>
         <v>26622.359023948273</v>
       </c>
-      <c r="M23" s="40">
+      <c r="M25" s="40">
         <f>M12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!M$6)</f>
         <v>34612.225529105635</v>
       </c>
-      <c r="N23" s="40">
+      <c r="N25" s="40">
         <f>N12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!N$6)</f>
         <v>45000</v>
       </c>
-      <c r="O23" s="40">
+      <c r="O25" s="40">
         <f>O12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!O$6)</f>
         <v>56584.504335732097</v>
       </c>
-      <c r="P23" s="40">
+      <c r="P25" s="40">
         <f>P12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!P$6)</f>
         <v>71151.247353788538</v>
       </c>
-      <c r="Q23" s="40">
+      <c r="Q25" s="40">
         <f>Q12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!Q$6)</f>
         <v>89467.956986293197</v>
       </c>
-      <c r="R23" s="40">
+      <c r="R25" s="40">
         <f>R12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!R$6)</f>
         <v>112500</v>
       </c>
-      <c r="S23" s="40">
+      <c r="S25" s="40">
         <f>S12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!S$6)</f>
         <v>133785.80043780612</v>
       </c>
-      <c r="T23" s="40">
+      <c r="T25" s="40">
         <f>T12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!T$6)</f>
         <v>159099.02576697321</v>
       </c>
-      <c r="U23" s="40">
+      <c r="U25" s="40">
         <f>U12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!U$6)</f>
         <v>189201.69343208577</v>
       </c>
-      <c r="V23" s="40">
+      <c r="V25" s="40">
         <f>V12*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!V$6)</f>
         <v>225000</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B24" s="9" t="s">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B26" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C24" s="40">
+      <c r="C26" s="40">
         <f>C12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!C$6)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="40">
+      <c r="D26" s="40">
         <f>D12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!D$6)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="40">
+      <c r="E26" s="40">
         <f>E12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!E$6)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F26" s="40">
         <f>F12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!F$6)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="40">
+      <c r="G26" s="40">
         <f>G12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!G$6)</f>
         <v>1025.8367999005354</v>
       </c>
-      <c r="H24" s="40">
+      <c r="H26" s="40">
         <f>H12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!H$6)</f>
         <v>1403.1215200402278</v>
       </c>
-      <c r="I24" s="40">
+      <c r="I26" s="40">
         <f>I12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!I$6)</f>
         <v>1919.1649199861897</v>
       </c>
-      <c r="J24" s="40">
+      <c r="J26" s="40">
         <f>J12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!J$6)</f>
         <v>2625</v>
       </c>
-      <c r="K24" s="40">
+      <c r="K26" s="40">
         <f>K12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!K$6)</f>
         <v>6825.6229233608765</v>
       </c>
-      <c r="L24" s="40">
+      <c r="L26" s="40">
         <f>L12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!L$6)</f>
         <v>8874.1196746494243</v>
       </c>
-      <c r="M24" s="40">
+      <c r="M26" s="40">
         <f>M12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!M$6)</f>
         <v>11537.408509701878</v>
       </c>
-      <c r="N24" s="40">
+      <c r="N26" s="40">
         <f>N12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!N$6)</f>
         <v>15000</v>
       </c>
-      <c r="O24" s="40">
+      <c r="O26" s="40">
         <f>O12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!O$6)</f>
         <v>18861.501445244034</v>
       </c>
-      <c r="P24" s="40">
+      <c r="P26" s="40">
         <f>P12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!P$6)</f>
         <v>23717.082451262846</v>
       </c>
-      <c r="Q24" s="40">
+      <c r="Q26" s="40">
         <f>Q12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!Q$6)</f>
         <v>29822.652328764398</v>
       </c>
-      <c r="R24" s="40">
+      <c r="R26" s="40">
         <f>R12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!R$6)</f>
         <v>37500</v>
       </c>
-      <c r="S24" s="40">
+      <c r="S26" s="40">
         <f>S12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!S$6)</f>
         <v>44595.266812602036</v>
       </c>
-      <c r="T24" s="40">
+      <c r="T26" s="40">
         <f>T12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!T$6)</f>
         <v>53033.00858899107</v>
       </c>
-      <c r="U24" s="40">
+      <c r="U26" s="40">
         <f>U12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!U$6)</f>
         <v>63067.231144028585</v>
       </c>
-      <c r="V24" s="40">
+      <c r="V26" s="40">
         <f>V12*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!V$6)</f>
         <v>75000</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B25" s="9" t="s">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B27" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C25" s="40">
+      <c r="C27" s="40">
         <f>C12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!C$6)</f>
         <v>177.82794100389231</v>
       </c>
-      <c r="D25" s="40">
+      <c r="D27" s="40">
         <f>D12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!D$6)</f>
         <v>316.22776601683796</v>
       </c>
-      <c r="E25" s="40">
+      <c r="E27" s="40">
         <f>E12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!E$6)</f>
         <v>562.34132519034927</v>
       </c>
-      <c r="F25" s="40">
+      <c r="F27" s="40">
         <f>F12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!F$6)</f>
         <v>1000</v>
       </c>
-      <c r="G25" s="40">
+      <c r="G27" s="40">
         <f>G12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!G$6)</f>
         <v>1025.8367999005354</v>
       </c>
-      <c r="H25" s="40">
+      <c r="H27" s="40">
         <f>H12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!H$6)</f>
         <v>1403.1215200402278</v>
       </c>
-      <c r="I25" s="40">
+      <c r="I27" s="40">
         <f>I12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!I$6)</f>
         <v>1919.1649199861897</v>
       </c>
-      <c r="J25" s="40">
+      <c r="J27" s="40">
         <f>J12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!J$6)</f>
         <v>2625</v>
       </c>
-      <c r="K25" s="40">
+      <c r="K27" s="40">
         <f>K12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!K$6)</f>
         <v>2275.207641120292</v>
       </c>
-      <c r="L25" s="40">
+      <c r="L27" s="40">
         <f>L12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!L$6)</f>
         <v>2958.0398915498081</v>
       </c>
-      <c r="M25" s="40">
+      <c r="M27" s="40">
         <f>M12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!M$6)</f>
         <v>3845.8028365672931</v>
       </c>
-      <c r="N25" s="40">
+      <c r="N27" s="40">
         <f>N12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!N$6)</f>
         <v>5000</v>
       </c>
-      <c r="O25" s="40">
+      <c r="O27" s="40">
         <f>O12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!O$6)</f>
         <v>6287.1671484146782</v>
       </c>
-      <c r="P25" s="40">
+      <c r="P27" s="40">
         <f>P12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!P$6)</f>
         <v>7905.6941504209499</v>
       </c>
-      <c r="Q25" s="40">
+      <c r="Q27" s="40">
         <f>Q12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!Q$6)</f>
         <v>9940.8841095881344</v>
       </c>
-      <c r="R25" s="40">
+      <c r="R27" s="40">
         <f>R12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!R$6)</f>
         <v>12500</v>
       </c>
-      <c r="S25" s="40">
+      <c r="S27" s="40">
         <f>S12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!S$6)</f>
         <v>14865.088937534014</v>
       </c>
-      <c r="T25" s="40">
+      <c r="T27" s="40">
         <f>T12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!T$6)</f>
         <v>17677.66952966369</v>
       </c>
-      <c r="U25" s="40">
+      <c r="U27" s="40">
         <f>U12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!U$6)</f>
         <v>21022.410381342866</v>
       </c>
-      <c r="V25" s="40">
+      <c r="V27" s="40">
         <f>V12*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!V$6)</f>
         <v>25000</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B28" s="9" t="s">
+    <row r="29" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B30" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="C28" s="40">
+      <c r="C30" s="40">
         <f>C14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!C$6)</f>
         <v>833.4838230116768</v>
       </c>
-      <c r="D28" s="40">
+      <c r="D30" s="40">
         <f>D14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!D$6)</f>
         <v>1482.1671210621907</v>
       </c>
-      <c r="E28" s="40">
+      <c r="E30" s="40">
         <f>E14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!E$6)</f>
         <v>2635.7072736215614</v>
       </c>
-      <c r="F28" s="40">
+      <c r="F30" s="40">
         <f>F14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!F$6)</f>
         <v>4687.0239755710472</v>
       </c>
-      <c r="G28" s="40">
+      <c r="G30" s="40">
         <f>G14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!G$6)</f>
         <v>5623.483199685028</v>
       </c>
-      <c r="H28" s="40">
+      <c r="H30" s="40">
         <f>H14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!H$6)</f>
         <v>7691.7013464790834</v>
       </c>
-      <c r="I28" s="40">
+      <c r="I30" s="40">
         <f>I14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!I$6)</f>
         <v>10520.573726750323</v>
       </c>
-      <c r="J28" s="40">
+      <c r="J30" s="40">
         <f>J14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!J$6)</f>
         <v>14389.855579956267</v>
       </c>
-      <c r="K28" s="40">
+      <c r="K30" s="40">
         <f>K14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!K$6)</f>
         <v>14088.226743921021</v>
       </c>
-      <c r="L28" s="40">
+      <c r="L30" s="40">
         <f>L14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!L$6)</f>
         <v>18316.366364345351</v>
       </c>
-      <c r="M28" s="40">
+      <c r="M30" s="40">
         <f>M14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!M$6)</f>
         <v>23813.449548409852</v>
       </c>
-      <c r="N28" s="40">
+      <c r="N30" s="40">
         <f>N14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!N$6)</f>
         <v>30960.309927985523</v>
       </c>
-      <c r="O28" s="40">
+      <c r="O30" s="40">
         <f>O14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!O$6)</f>
         <v>39505.08501945137</v>
       </c>
-      <c r="P28" s="40">
+      <c r="P30" s="40">
         <f>P14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!P$6)</f>
         <v>49675.014545924692</v>
       </c>
-      <c r="Q28" s="40">
+      <c r="Q30" s="40">
         <f>Q14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!Q$6)</f>
         <v>62463.023910031792</v>
       </c>
-      <c r="R28" s="40">
+      <c r="R30" s="40">
         <f>R14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!R$6)</f>
         <v>78543.094383558462</v>
       </c>
-      <c r="S28" s="40">
+      <c r="S30" s="40">
         <f>S14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!S$6)</f>
         <v>95777.811281369039</v>
       </c>
-      <c r="T28" s="40">
+      <c r="T30" s="40">
         <f>T14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!T$6)</f>
         <v>113899.65463519195</v>
       </c>
-      <c r="U28" s="40">
+      <c r="U30" s="40">
         <f>U14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!U$6)</f>
         <v>135450.27968852295</v>
       </c>
-      <c r="V28" s="40">
+      <c r="V30" s="40">
         <f>V14*INDEX(Assumptions!$C$35:$G$38,1,'Consumer Model'!V$6)</f>
         <v>161078.43633470003</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B29" s="9" t="s">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B31" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="40">
+      <c r="C31" s="40">
         <f>C14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!C$6)</f>
         <v>416.7419115058384</v>
       </c>
-      <c r="D29" s="40">
+      <c r="D31" s="40">
         <f>D14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!D$6)</f>
         <v>741.08356053109537</v>
       </c>
-      <c r="E29" s="40">
+      <c r="E31" s="40">
         <f>E14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!E$6)</f>
         <v>1317.8536368107807</v>
       </c>
-      <c r="F29" s="40">
+      <c r="F31" s="40">
         <f>F14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!F$6)</f>
         <v>2343.5119877855236</v>
       </c>
-      <c r="G29" s="40">
+      <c r="G31" s="40">
         <f>G14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!G$6)</f>
         <v>4439.5919997513383</v>
       </c>
-      <c r="H29" s="40">
+      <c r="H31" s="40">
         <f>H14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!H$6)</f>
         <v>6072.3957998519081</v>
       </c>
-      <c r="I29" s="40">
+      <c r="I31" s="40">
         <f>I14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!I$6)</f>
         <v>8305.7161000660453</v>
       </c>
-      <c r="J29" s="40">
+      <c r="J31" s="40">
         <f>J14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!J$6)</f>
         <v>11360.412299965476</v>
       </c>
-      <c r="K29" s="40">
+      <c r="K31" s="40">
         <f>K14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!K$6)</f>
         <v>18113.434385041313</v>
       </c>
-      <c r="L29" s="40">
+      <c r="L31" s="40">
         <f>L14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!L$6)</f>
         <v>23549.61389701545</v>
       </c>
-      <c r="M29" s="40">
+      <c r="M31" s="40">
         <f>M14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!M$6)</f>
         <v>30617.292276526954</v>
       </c>
-      <c r="N29" s="40">
+      <c r="N31" s="40">
         <f>N14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!N$6)</f>
         <v>39806.112764552818</v>
       </c>
-      <c r="O29" s="40">
+      <c r="O31" s="40">
         <f>O14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!O$6)</f>
         <v>50792.252167866049</v>
       </c>
-      <c r="P29" s="40">
+      <c r="P31" s="40">
         <f>P14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!P$6)</f>
         <v>63867.875844760325</v>
       </c>
-      <c r="Q29" s="40">
+      <c r="Q31" s="40">
         <f>Q14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!Q$6)</f>
         <v>80309.602170040875</v>
       </c>
-      <c r="R29" s="40">
+      <c r="R31" s="40">
         <f>R14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!R$6)</f>
         <v>100983.9784931466</v>
       </c>
-      <c r="S29" s="40">
+      <c r="S31" s="40">
         <f>S14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!S$6)</f>
         <v>123142.90021890306</v>
       </c>
-      <c r="T29" s="40">
+      <c r="T31" s="40">
         <f>T14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!T$6)</f>
         <v>146442.41310238966</v>
       </c>
-      <c r="U29" s="40">
+      <c r="U31" s="40">
         <f>U14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!U$6)</f>
         <v>174150.3595995295</v>
       </c>
-      <c r="V29" s="40">
+      <c r="V31" s="40">
         <f>V14*INDEX(Assumptions!$C$35:$G$38,2,'Consumer Model'!V$6)</f>
         <v>207100.8467160429</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B30" s="9" t="s">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B32" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C30" s="40">
+      <c r="C32" s="40">
         <f>C14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!C$6)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="40">
+      <c r="D32" s="40">
         <f>D14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!D$6)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="40">
+      <c r="E32" s="40">
         <f>E14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!E$6)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="40">
+      <c r="F32" s="40">
         <f>F14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!F$6)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="40">
+      <c r="G32" s="40">
         <f>G14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!G$6)</f>
         <v>887.9183999502676</v>
       </c>
-      <c r="H30" s="40">
+      <c r="H32" s="40">
         <f>H14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!H$6)</f>
         <v>1214.4791599703815</v>
       </c>
-      <c r="I30" s="40">
+      <c r="I32" s="40">
         <f>I14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!I$6)</f>
         <v>1661.1432200132087</v>
       </c>
-      <c r="J30" s="40">
+      <c r="J32" s="40">
         <f>J14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!J$6)</f>
         <v>2272.0824599930947</v>
       </c>
-      <c r="K30" s="40">
+      <c r="K32" s="40">
         <f>K14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!K$6)</f>
         <v>6037.8114616804378</v>
       </c>
-      <c r="L30" s="40">
+      <c r="L32" s="40">
         <f>L14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!L$6)</f>
         <v>7849.8712990051499</v>
       </c>
-      <c r="M30" s="40">
+      <c r="M32" s="40">
         <f>M14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!M$6)</f>
         <v>10205.764092175652</v>
       </c>
-      <c r="N30" s="40">
+      <c r="N32" s="40">
         <f>N14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!N$6)</f>
         <v>13268.70425485094</v>
       </c>
-      <c r="O30" s="40">
+      <c r="O32" s="40">
         <f>O14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!O$6)</f>
         <v>16930.750722622015</v>
       </c>
-      <c r="P30" s="40">
+      <c r="P32" s="40">
         <f>P14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!P$6)</f>
         <v>21289.291948253438</v>
       </c>
-      <c r="Q30" s="40">
+      <c r="Q32" s="40">
         <f>Q14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!Q$6)</f>
         <v>26769.867390013624</v>
       </c>
-      <c r="R30" s="40">
+      <c r="R32" s="40">
         <f>R14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!R$6)</f>
         <v>33661.326164382197</v>
       </c>
-      <c r="S30" s="40">
+      <c r="S32" s="40">
         <f>S14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!S$6)</f>
         <v>41047.633406301022</v>
       </c>
-      <c r="T30" s="40">
+      <c r="T32" s="40">
         <f>T14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!T$6)</f>
         <v>48814.137700796557</v>
       </c>
-      <c r="U30" s="40">
+      <c r="U32" s="40">
         <f>U14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!U$6)</f>
         <v>58050.119866509835</v>
       </c>
-      <c r="V30" s="40">
+      <c r="V32" s="40">
         <f>V14*INDEX(Assumptions!$C$35:$G$38,3,'Consumer Model'!V$6)</f>
         <v>69033.6155720143</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B31" s="9" t="s">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B33" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C31" s="40">
+      <c r="C33" s="40">
         <f>C14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!C$6)</f>
         <v>138.91397050194615</v>
       </c>
-      <c r="D31" s="40">
+      <c r="D33" s="40">
         <f>D14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!D$6)</f>
         <v>247.02785351036516</v>
       </c>
-      <c r="E31" s="40">
+      <c r="E33" s="40">
         <f>E14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!E$6)</f>
         <v>439.28454560359364</v>
       </c>
-      <c r="F31" s="40">
+      <c r="F33" s="40">
         <f>F14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!F$6)</f>
         <v>781.17066259517469</v>
       </c>
-      <c r="G31" s="40">
+      <c r="G33" s="40">
         <f>G14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!G$6)</f>
         <v>887.9183999502676</v>
       </c>
-      <c r="H31" s="40">
+      <c r="H33" s="40">
         <f>H14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!H$6)</f>
         <v>1214.4791599703815</v>
       </c>
-      <c r="I31" s="40">
+      <c r="I33" s="40">
         <f>I14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!I$6)</f>
         <v>1661.1432200132087</v>
       </c>
-      <c r="J31" s="40">
+      <c r="J33" s="40">
         <f>J14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!J$6)</f>
         <v>2272.0824599930947</v>
       </c>
-      <c r="K31" s="40">
+      <c r="K33" s="40">
         <f>K14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!K$6)</f>
         <v>2012.6038205601462</v>
       </c>
-      <c r="L31" s="40">
+      <c r="L33" s="40">
         <f>L14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!L$6)</f>
         <v>2616.6237663350503</v>
       </c>
-      <c r="M31" s="40">
+      <c r="M33" s="40">
         <f>M14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!M$6)</f>
         <v>3401.9213640585508</v>
       </c>
-      <c r="N31" s="40">
+      <c r="N33" s="40">
         <f>N14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!N$6)</f>
         <v>4422.9014182836463</v>
       </c>
-      <c r="O31" s="40">
+      <c r="O33" s="40">
         <f>O14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!O$6)</f>
         <v>5643.5835742073396</v>
       </c>
-      <c r="P31" s="40">
+      <c r="P33" s="40">
         <f>P14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!P$6)</f>
         <v>7096.4306494178136</v>
       </c>
-      <c r="Q31" s="40">
+      <c r="Q33" s="40">
         <f>Q14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!Q$6)</f>
         <v>8923.289130004543</v>
       </c>
-      <c r="R31" s="40">
+      <c r="R33" s="40">
         <f>R14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!R$6)</f>
         <v>11220.442054794068</v>
       </c>
-      <c r="S31" s="40">
+      <c r="S33" s="40">
         <f>S14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!S$6)</f>
         <v>13682.544468767008</v>
       </c>
-      <c r="T31" s="40">
+      <c r="T33" s="40">
         <f>T14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!T$6)</f>
         <v>16271.379233598853</v>
       </c>
-      <c r="U31" s="40">
+      <c r="U33" s="40">
         <f>U14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!U$6)</f>
         <v>19350.039955503278</v>
       </c>
-      <c r="V31" s="40">
+      <c r="V33" s="40">
         <f>V14*INDEX(Assumptions!$C$35:$G$38,4,'Consumer Model'!V$6)</f>
         <v>23011.205190671433</v>
       </c>
@@ -4687,7 +4783,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4699,7 +4795,7 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
@@ -4919,7 +5015,7 @@
     </row>
     <row r="9" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -4931,92 +5027,92 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B10" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C10" s="40">
-        <f>'Consumer Model'!C22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!C$6)</f>
+        <f>'Consumer Model'!C24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!C$6)</f>
         <v>0</v>
       </c>
       <c r="D10" s="40">
-        <f>'Consumer Model'!D22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!D$6)</f>
+        <f>'Consumer Model'!D24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!D$6)</f>
         <v>0</v>
       </c>
       <c r="E10" s="40">
-        <f>'Consumer Model'!E22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!E$6)</f>
+        <f>'Consumer Model'!E24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!E$6)</f>
         <v>0</v>
       </c>
       <c r="F10" s="40">
-        <f>'Consumer Model'!F22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!F$6)</f>
+        <f>'Consumer Model'!F24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!F$6)</f>
         <v>0</v>
       </c>
       <c r="G10" s="40">
-        <f>'Consumer Model'!G22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!G$6)</f>
+        <f>'Consumer Model'!G24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!G$6)</f>
         <v>233.89079037732208</v>
       </c>
       <c r="H10" s="40">
-        <f>'Consumer Model'!H22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!H$6)</f>
+        <f>'Consumer Model'!H24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!H$6)</f>
         <v>319.91170656917194</v>
       </c>
       <c r="I10" s="40">
-        <f>'Consumer Model'!I22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!I$6)</f>
+        <f>'Consumer Model'!I24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!I$6)</f>
         <v>437.56960175685123</v>
       </c>
       <c r="J10" s="40">
-        <f>'Consumer Model'!J22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!J$6)</f>
+        <f>'Consumer Model'!J24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!J$6)</f>
         <v>598.5</v>
       </c>
       <c r="K10" s="40">
-        <f>'Consumer Model'!K22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!K$6)</f>
+        <f>'Consumer Model'!K24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!K$6)</f>
         <v>891.88139531915442</v>
       </c>
       <c r="L10" s="40">
-        <f>'Consumer Model'!L22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!L$6)</f>
+        <f>'Consumer Model'!L24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!L$6)</f>
         <v>1159.5516374875247</v>
       </c>
       <c r="M10" s="40">
-        <f>'Consumer Model'!M22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!M$6)</f>
+        <f>'Consumer Model'!M24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!M$6)</f>
         <v>1507.5547119343787</v>
       </c>
       <c r="N10" s="40">
-        <f>'Consumer Model'!N22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!N$6)</f>
+        <f>'Consumer Model'!N24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!N$6)</f>
         <v>1959.9999999999998</v>
       </c>
       <c r="O10" s="40">
-        <f>'Consumer Model'!O22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!O$6)</f>
+        <f>'Consumer Model'!O24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!O$6)</f>
         <v>3168.7322428009975</v>
       </c>
       <c r="P10" s="40">
-        <f>'Consumer Model'!P22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!P$6)</f>
+        <f>'Consumer Model'!P24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!P$6)</f>
         <v>3984.4698518121586</v>
       </c>
       <c r="Q10" s="40">
-        <f>'Consumer Model'!Q22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!Q$6)</f>
+        <f>'Consumer Model'!Q24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!Q$6)</f>
         <v>5010.2055912324186</v>
       </c>
       <c r="R10" s="40">
-        <f>'Consumer Model'!R22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!R$6)</f>
+        <f>'Consumer Model'!R24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!R$6)</f>
         <v>6300</v>
       </c>
       <c r="S10" s="40">
-        <f>'Consumer Model'!S22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!S$6)</f>
+        <f>'Consumer Model'!S24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!S$6)</f>
         <v>8324.4498050190468</v>
       </c>
       <c r="T10" s="40">
-        <f>'Consumer Model'!T22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!T$6)</f>
+        <f>'Consumer Model'!T24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!T$6)</f>
         <v>9899.4949366116653</v>
       </c>
       <c r="U10" s="40">
-        <f>'Consumer Model'!U22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!U$6)</f>
+        <f>'Consumer Model'!U24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!U$6)</f>
         <v>11772.549813552003</v>
       </c>
       <c r="V10" s="40">
-        <f>'Consumer Model'!V22*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!V$6)</f>
+        <f>'Consumer Model'!V24*Assumptions!$F$21*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!V$6)</f>
         <v>14000</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B11" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C11" s="40">
         <f>C10</f>
@@ -5101,7 +5197,7 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B12" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C12" s="16">
         <f>0</f>
@@ -5186,7 +5282,7 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B13" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C13" s="16">
         <f>C11*Assumptions!$D$21*Assumptions!$H$21</f>
@@ -5271,7 +5367,7 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B14" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C14" s="16">
         <f>C10*Assumptions!$D$21*Assumptions!$G$21*3</f>
@@ -5356,7 +5452,7 @@
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B15" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C15" s="16">
         <f>-C12*Assumptions!$C$14/4</f>
@@ -5441,7 +5537,7 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B16" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C16" s="16">
         <f>-C12*(1-(1-Assumptions!$E$21)^3)</f>
@@ -5526,7 +5622,7 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C17" s="16">
         <f>(C12+(C13+C14)/2)*((1+Assumptions!$C$13)^(1/4)-1)</f>
@@ -5611,7 +5707,7 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B18" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C18" s="43">
         <f t="shared" ref="C18:V18" si="3">C12+C13+C14+C15+C16+C17</f>
@@ -5696,7 +5792,7 @@
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B19" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C19" s="16">
         <f t="shared" ref="C19:V19" si="4">(C12+C18)/2</f>
@@ -5781,7 +5877,7 @@
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B20" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C20" s="16">
         <f t="shared" ref="C20:V20" si="5">IF(C10=0,0,C18/C10)</f>
@@ -5866,7 +5962,7 @@
     </row>
     <row r="22" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -5878,92 +5974,92 @@
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B23" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C23" s="40">
-        <f>'Consumer Model'!C23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!C$6)</f>
+        <f>'Consumer Model'!C25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!C$6)</f>
         <v>0</v>
       </c>
       <c r="D23" s="40">
-        <f>'Consumer Model'!D23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!D$6)</f>
+        <f>'Consumer Model'!D25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!D$6)</f>
         <v>0</v>
       </c>
       <c r="E23" s="40">
-        <f>'Consumer Model'!E23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!E$6)</f>
+        <f>'Consumer Model'!E25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!E$6)</f>
         <v>0</v>
       </c>
       <c r="F23" s="40">
-        <f>'Consumer Model'!F23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!F$6)</f>
+        <f>'Consumer Model'!F25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!F$6)</f>
         <v>0</v>
       </c>
       <c r="G23" s="40">
-        <f>'Consumer Model'!G23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!G$6)</f>
+        <f>'Consumer Model'!G25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!G$6)</f>
         <v>577.03319994405126</v>
       </c>
       <c r="H23" s="40">
-        <f>'Consumer Model'!H23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!H$6)</f>
+        <f>'Consumer Model'!H25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!H$6)</f>
         <v>789.25585502262823</v>
       </c>
       <c r="I23" s="40">
-        <f>'Consumer Model'!I23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!I$6)</f>
+        <f>'Consumer Model'!I25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!I$6)</f>
         <v>1079.5302674922318</v>
       </c>
       <c r="J23" s="40">
-        <f>'Consumer Model'!J23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!J$6)</f>
+        <f>'Consumer Model'!J25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!J$6)</f>
         <v>1476.5625</v>
       </c>
       <c r="K23" s="40">
-        <f>'Consumer Model'!K23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!K$6)</f>
+        <f>'Consumer Model'!K25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!K$6)</f>
         <v>3583.4520347644602</v>
       </c>
       <c r="L23" s="40">
-        <f>'Consumer Model'!L23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!L$6)</f>
+        <f>'Consumer Model'!L25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!L$6)</f>
         <v>4658.9128291909474</v>
       </c>
       <c r="M23" s="40">
-        <f>'Consumer Model'!M23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!M$6)</f>
+        <f>'Consumer Model'!M25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!M$6)</f>
         <v>6057.1394675934862</v>
       </c>
       <c r="N23" s="40">
-        <f>'Consumer Model'!N23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!N$6)</f>
+        <f>'Consumer Model'!N25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!N$6)</f>
         <v>7874.9999999999991</v>
       </c>
       <c r="O23" s="40">
-        <f>'Consumer Model'!O23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!O$6)</f>
+        <f>'Consumer Model'!O25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!O$6)</f>
         <v>12731.513475539723</v>
       </c>
       <c r="P23" s="40">
-        <f>'Consumer Model'!P23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!P$6)</f>
+        <f>'Consumer Model'!P25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!P$6)</f>
         <v>16009.030654602422</v>
       </c>
       <c r="Q23" s="40">
-        <f>'Consumer Model'!Q23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!Q$6)</f>
+        <f>'Consumer Model'!Q25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!Q$6)</f>
         <v>20130.290321915971</v>
       </c>
       <c r="R23" s="40">
-        <f>'Consumer Model'!R23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!R$6)</f>
+        <f>'Consumer Model'!R25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!R$6)</f>
         <v>25312.5</v>
       </c>
       <c r="S23" s="40">
-        <f>'Consumer Model'!S23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!S$6)</f>
+        <f>'Consumer Model'!S25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!S$6)</f>
         <v>33446.450109451529</v>
       </c>
       <c r="T23" s="40">
-        <f>'Consumer Model'!T23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!T$6)</f>
+        <f>'Consumer Model'!T25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!T$6)</f>
         <v>39774.756441743302</v>
       </c>
       <c r="U23" s="40">
-        <f>'Consumer Model'!U23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!U$6)</f>
+        <f>'Consumer Model'!U25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!U$6)</f>
         <v>47300.423358021442</v>
       </c>
       <c r="V23" s="40">
-        <f>'Consumer Model'!V23*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!V$6)</f>
+        <f>'Consumer Model'!V25*Assumptions!$F$22*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!V$6)</f>
         <v>56250</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B24" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C24" s="40">
         <f>C23</f>
@@ -6048,7 +6144,7 @@
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B25" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C25" s="16">
         <f>0</f>
@@ -6133,7 +6229,7 @@
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B26" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C26" s="16">
         <f>C24*Assumptions!$D$22*Assumptions!$H$22</f>
@@ -6218,7 +6314,7 @@
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B27" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C27" s="16">
         <f>C23*Assumptions!$D$22*Assumptions!$G$22*3</f>
@@ -6303,7 +6399,7 @@
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B28" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C28" s="16">
         <f>-C25*Assumptions!$C$14/4</f>
@@ -6388,7 +6484,7 @@
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B29" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C29" s="16">
         <f>-C25*(1-(1-Assumptions!$E$22)^3)</f>
@@ -6473,7 +6569,7 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B30" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C30" s="16">
         <f>(C25+(C26+C27)/2)*((1+Assumptions!$C$13)^(1/4)-1)</f>
@@ -6558,7 +6654,7 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B31" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C31" s="43">
         <f t="shared" ref="C31:V31" si="8">C25+C26+C27+C28+C29+C30</f>
@@ -6643,7 +6739,7 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B32" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C32" s="16">
         <f t="shared" ref="C32:V32" si="9">(C25+C31)/2</f>
@@ -6728,7 +6824,7 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B33" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C33" s="16">
         <f t="shared" ref="C33:V33" si="10">IF(C23=0,0,C31/C23)</f>
@@ -6813,7 +6909,7 @@
     </row>
     <row r="35" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -6825,92 +6921,92 @@
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B36" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C36" s="40">
-        <f>'Consumer Model'!C24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!C$6)</f>
+        <f>'Consumer Model'!C26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!C$6)</f>
         <v>0</v>
       </c>
       <c r="D36" s="40">
-        <f>'Consumer Model'!D24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!D$6)</f>
+        <f>'Consumer Model'!D26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!D$6)</f>
         <v>0</v>
       </c>
       <c r="E36" s="40">
-        <f>'Consumer Model'!E24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!E$6)</f>
+        <f>'Consumer Model'!E26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!E$6)</f>
         <v>0</v>
       </c>
       <c r="F36" s="40">
-        <f>'Consumer Model'!F24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!F$6)</f>
+        <f>'Consumer Model'!F26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!F$6)</f>
         <v>0</v>
       </c>
       <c r="G36" s="40">
-        <f>'Consumer Model'!G24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!G$6)</f>
+        <f>'Consumer Model'!G26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!G$6)</f>
         <v>184.65062398209639</v>
       </c>
       <c r="H36" s="40">
-        <f>'Consumer Model'!H24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!H$6)</f>
+        <f>'Consumer Model'!H26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!H$6)</f>
         <v>252.56187360724101</v>
       </c>
       <c r="I36" s="40">
-        <f>'Consumer Model'!I24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!I$6)</f>
+        <f>'Consumer Model'!I26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!I$6)</f>
         <v>345.44968559751419</v>
       </c>
       <c r="J36" s="40">
-        <f>'Consumer Model'!J24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!J$6)</f>
+        <f>'Consumer Model'!J26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!J$6)</f>
         <v>472.5</v>
       </c>
       <c r="K36" s="40">
-        <f>'Consumer Model'!K24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!K$6)</f>
+        <f>'Consumer Model'!K26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!K$6)</f>
         <v>1911.1744185410455</v>
       </c>
       <c r="L36" s="40">
-        <f>'Consumer Model'!L24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!L$6)</f>
+        <f>'Consumer Model'!L26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!L$6)</f>
         <v>2484.7535089018388</v>
       </c>
       <c r="M36" s="40">
-        <f>'Consumer Model'!M24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!M$6)</f>
+        <f>'Consumer Model'!M26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!M$6)</f>
         <v>3230.4743827165262</v>
       </c>
       <c r="N36" s="40">
-        <f>'Consumer Model'!N24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!N$6)</f>
+        <f>'Consumer Model'!N26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!N$6)</f>
         <v>4200</v>
       </c>
       <c r="O36" s="40">
-        <f>'Consumer Model'!O24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!O$6)</f>
+        <f>'Consumer Model'!O26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!O$6)</f>
         <v>6790.1405202878523</v>
       </c>
       <c r="P36" s="40">
-        <f>'Consumer Model'!P24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!P$6)</f>
+        <f>'Consumer Model'!P26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!P$6)</f>
         <v>8538.1496824546248</v>
       </c>
       <c r="Q36" s="40">
-        <f>'Consumer Model'!Q24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!Q$6)</f>
+        <f>'Consumer Model'!Q26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!Q$6)</f>
         <v>10736.154838355184</v>
       </c>
       <c r="R36" s="40">
-        <f>'Consumer Model'!R24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!R$6)</f>
+        <f>'Consumer Model'!R26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!R$6)</f>
         <v>13500</v>
       </c>
       <c r="S36" s="40">
-        <f>'Consumer Model'!S24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!S$6)</f>
+        <f>'Consumer Model'!S26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!S$6)</f>
         <v>17838.106725040816</v>
       </c>
       <c r="T36" s="40">
-        <f>'Consumer Model'!T24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!T$6)</f>
+        <f>'Consumer Model'!T26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!T$6)</f>
         <v>21213.203435596428</v>
       </c>
       <c r="U36" s="40">
-        <f>'Consumer Model'!U24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!U$6)</f>
+        <f>'Consumer Model'!U26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!U$6)</f>
         <v>25226.892457611437</v>
       </c>
       <c r="V36" s="40">
-        <f>'Consumer Model'!V24*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!V$6)</f>
+        <f>'Consumer Model'!V26*Assumptions!$F$23*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!V$6)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B37" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C37" s="40">
         <f>C36</f>
@@ -6995,7 +7091,7 @@
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B38" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C38" s="16">
         <f>0</f>
@@ -7080,7 +7176,7 @@
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B39" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C39" s="16">
         <f>C37*Assumptions!$D$23*Assumptions!$H$23</f>
@@ -7165,7 +7261,7 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B40" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C40" s="16">
         <f>C36*Assumptions!$D$23*Assumptions!$G$23*3</f>
@@ -7250,7 +7346,7 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B41" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C41" s="16">
         <f>-C38*Assumptions!$C$14/4</f>
@@ -7335,7 +7431,7 @@
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B42" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C42" s="16">
         <f>-C38*(1-(1-Assumptions!$E$23)^3)</f>
@@ -7420,7 +7516,7 @@
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B43" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C43" s="16">
         <f>(C38+(C39+C40)/2)*((1+Assumptions!$C$13)^(1/4)-1)</f>
@@ -7505,7 +7601,7 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B44" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C44" s="43">
         <f t="shared" ref="C44:V44" si="13">C38+C39+C40+C41+C42+C43</f>
@@ -7590,7 +7686,7 @@
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B45" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C45" s="16">
         <f t="shared" ref="C45:V45" si="14">(C38+C44)/2</f>
@@ -7675,7 +7771,7 @@
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B46" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C46" s="16">
         <f t="shared" ref="C46:V46" si="15">IF(C36=0,0,C44/C36)</f>
@@ -7760,7 +7856,7 @@
     </row>
     <row r="48" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -7772,92 +7868,92 @@
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B49" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C49" s="40">
-        <f>'Consumer Model'!C25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!C$6)</f>
+        <f>'Consumer Model'!C27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!C$6)</f>
         <v>0</v>
       </c>
       <c r="D49" s="40">
-        <f>'Consumer Model'!D25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!D$6)</f>
+        <f>'Consumer Model'!D27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!D$6)</f>
         <v>0</v>
       </c>
       <c r="E49" s="40">
-        <f>'Consumer Model'!E25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!E$6)</f>
+        <f>'Consumer Model'!E27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!E$6)</f>
         <v>0</v>
       </c>
       <c r="F49" s="40">
-        <f>'Consumer Model'!F25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!F$6)</f>
+        <f>'Consumer Model'!F27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!F$6)</f>
         <v>0</v>
       </c>
       <c r="G49" s="40">
-        <f>'Consumer Model'!G25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!G$6)</f>
+        <f>'Consumer Model'!G27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!G$6)</f>
         <v>323.13859196866861</v>
       </c>
       <c r="H49" s="40">
-        <f>'Consumer Model'!H25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!H$6)</f>
+        <f>'Consumer Model'!H27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!H$6)</f>
         <v>441.9832788126717</v>
       </c>
       <c r="I49" s="40">
-        <f>'Consumer Model'!I25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!I$6)</f>
+        <f>'Consumer Model'!I27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!I$6)</f>
         <v>604.53694979564978</v>
       </c>
       <c r="J49" s="40">
-        <f>'Consumer Model'!J25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!J$6)</f>
+        <f>'Consumer Model'!J27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!J$6)</f>
         <v>826.87499999999989</v>
       </c>
       <c r="K49" s="40">
-        <f>'Consumer Model'!K25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!K$6)</f>
+        <f>'Consumer Model'!K27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!K$6)</f>
         <v>1114.851744148943</v>
       </c>
       <c r="L49" s="40">
-        <f>'Consumer Model'!L25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!L$6)</f>
+        <f>'Consumer Model'!L27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!L$6)</f>
         <v>1449.4395468594059</v>
       </c>
       <c r="M49" s="40">
-        <f>'Consumer Model'!M25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!M$6)</f>
+        <f>'Consumer Model'!M27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!M$6)</f>
         <v>1884.4433899179733</v>
       </c>
       <c r="N49" s="40">
-        <f>'Consumer Model'!N25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!N$6)</f>
+        <f>'Consumer Model'!N27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!N$6)</f>
         <v>2450</v>
       </c>
       <c r="O49" s="40">
-        <f>'Consumer Model'!O25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!O$6)</f>
+        <f>'Consumer Model'!O27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!O$6)</f>
         <v>3960.9153035012469</v>
       </c>
       <c r="P49" s="40">
-        <f>'Consumer Model'!P25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!P$6)</f>
+        <f>'Consumer Model'!P27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!P$6)</f>
         <v>4980.5873147651982</v>
       </c>
       <c r="Q49" s="40">
-        <f>'Consumer Model'!Q25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!Q$6)</f>
+        <f>'Consumer Model'!Q27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!Q$6)</f>
         <v>6262.7569890405248</v>
       </c>
       <c r="R49" s="40">
-        <f>'Consumer Model'!R25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!R$6)</f>
+        <f>'Consumer Model'!R27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!R$6)</f>
         <v>7875</v>
       </c>
       <c r="S49" s="40">
-        <f>'Consumer Model'!S25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!S$6)</f>
+        <f>'Consumer Model'!S27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!S$6)</f>
         <v>10405.56225627381</v>
       </c>
       <c r="T49" s="40">
-        <f>'Consumer Model'!T25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!T$6)</f>
+        <f>'Consumer Model'!T27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!T$6)</f>
         <v>12374.368670764583</v>
       </c>
       <c r="U49" s="40">
-        <f>'Consumer Model'!U25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!U$6)</f>
+        <f>'Consumer Model'!U27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!U$6)</f>
         <v>14715.687266940005</v>
       </c>
       <c r="V49" s="40">
-        <f>'Consumer Model'!V25*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!V$6)</f>
+        <f>'Consumer Model'!V27*Assumptions!$F$24*INDEX(Assumptions!$C$16:$G$16,1,'Consumer Model'!V$6)</f>
         <v>17500</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B50" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C50" s="40">
         <f>C49</f>
@@ -7942,7 +8038,7 @@
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B51" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C51" s="16">
         <f>0</f>
@@ -8027,7 +8123,7 @@
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B52" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C52" s="16">
         <f>C50*Assumptions!$D$24*Assumptions!$H$24</f>
@@ -8112,7 +8208,7 @@
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B53" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C53" s="16">
         <f>C49*Assumptions!$D$24*Assumptions!$G$24*3</f>
@@ -8197,7 +8293,7 @@
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B54" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C54" s="16">
         <f>-C51*Assumptions!$C$14/4</f>
@@ -8282,7 +8378,7 @@
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B55" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C55" s="16">
         <f>-C51*(1-(1-Assumptions!$E$24)^3)</f>
@@ -8367,7 +8463,7 @@
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B56" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C56" s="16">
         <f>(C51+(C52+C53)/2)*((1+Assumptions!$C$13)^(1/4)-1)</f>
@@ -8452,7 +8548,7 @@
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B57" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C57" s="43">
         <f t="shared" ref="C57:V57" si="18">C51+C52+C53+C54+C55+C56</f>
@@ -8537,7 +8633,7 @@
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B58" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C58" s="16">
         <f t="shared" ref="C58:V58" si="19">(C51+C57)/2</f>
@@ -8622,7 +8718,7 @@
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B59" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C59" s="16">
         <f t="shared" ref="C59:V59" si="20">IF(C49=0,0,C57/C49)</f>
@@ -8707,7 +8803,7 @@
     </row>
     <row r="61" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -8719,7 +8815,7 @@
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B62" s="7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C62" s="44">
         <f t="shared" ref="C62:V62" si="21">C10+C23+C36+C49</f>
@@ -8804,7 +8900,7 @@
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B63" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C63" s="16">
         <f t="shared" ref="C63:V63" si="22">C13+C26+C39+C52</f>
@@ -8889,7 +8985,7 @@
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B64" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C64" s="16">
         <f t="shared" ref="C64:V64" si="23">C14+C27+C40+C53</f>
@@ -8974,7 +9070,7 @@
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B65" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C65" s="16">
         <f t="shared" ref="C65:V65" si="24">C15+C28+C41+C54</f>
@@ -9059,7 +9155,7 @@
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B66" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C66" s="16">
         <f t="shared" ref="C66:V66" si="25">C16+C29+C42+C55</f>
@@ -9144,7 +9240,7 @@
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B67" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C67" s="16">
         <f t="shared" ref="C67:V67" si="26">C17+C30+C43+C56</f>
@@ -9229,7 +9325,7 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B68" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C68" s="45">
         <f t="shared" ref="C68:V68" si="27">C18+C31+C44+C57</f>
@@ -9314,7 +9410,7 @@
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B69" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C69" s="16">
         <f t="shared" ref="C69:V69" si="28">C19+C32+C45+C58</f>
@@ -9399,7 +9495,7 @@
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B70" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C70" s="15">
         <f t="shared" ref="C70:V70" si="29">IF(C62=0,0,C68/C62)</f>
@@ -9484,7 +9580,7 @@
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B71" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C71" s="17">
         <f>C62/'Consumer Model'!C12</f>
@@ -9569,7 +9665,7 @@
     </row>
     <row r="73" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -9581,7 +9677,7 @@
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B74" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C74" s="43">
         <f>C69*Assumptions!$C$12/4</f>
@@ -9666,7 +9762,7 @@
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B75" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C75" s="16">
         <f>C68*Assumptions!$C$12</f>
@@ -9766,7 +9862,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9778,7 +9874,7 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
@@ -9998,7 +10094,7 @@
     </row>
     <row r="9" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -10010,7 +10106,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B10" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C10" s="16">
         <f>'Consumer Model'!C19</f>
@@ -10095,7 +10191,7 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B11" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C11" s="16">
         <f>C10*Assumptions!$C$5/4</f>
@@ -10180,7 +10276,7 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B12" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C12" s="16">
         <f>-C11*Assumptions!$C$7</f>
@@ -10265,7 +10361,7 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B13" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C13" s="43">
         <f>C11*Assumptions!$C$6</f>
@@ -10350,7 +10446,7 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B14" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C14" s="16">
         <f>C10*Assumptions!$C$47*3</f>
@@ -10435,7 +10531,7 @@
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B15" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C15" s="16">
         <f>C14*Assumptions!$C$48*Assumptions!$C$50</f>
@@ -10520,7 +10616,7 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B16" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C16" s="16">
         <f>C14*Assumptions!$C$49*Assumptions!$C$51-C14*Assumptions!$C$49/Assumptions!$C$53*Assumptions!$C$52</f>
@@ -10605,7 +10701,7 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B17" s="7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C17" s="15">
         <f t="shared" ref="C17:V17" si="1">C15+C16</f>
@@ -10690,7 +10786,7 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B18" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C18" s="43">
         <f>'AUM Engine'!C74</f>
@@ -10775,7 +10871,7 @@
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B19" s="7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C19" s="45">
         <f t="shared" ref="C19:V19" si="2">C13+C17+C18</f>
@@ -10860,7 +10956,7 @@
     </row>
     <row r="21" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -10872,7 +10968,7 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B22" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C22" s="17">
         <f t="shared" ref="C22:V22" si="3">C13/C19</f>
@@ -10957,7 +11053,7 @@
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B23" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C23" s="17">
         <f t="shared" ref="C23:V23" si="4">C17/C19</f>
@@ -11042,7 +11138,7 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B24" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C24" s="36">
         <f t="shared" ref="C24:V24" si="5">C18/C19</f>
@@ -11127,7 +11223,7 @@
     </row>
     <row r="26" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -11139,7 +11235,7 @@
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B27" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C27" s="8">
         <f t="shared" ref="C27:V27" si="6">IF(C13=0,0,C18/C13)</f>
@@ -11224,7 +11320,7 @@
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B28" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C28" s="9" t="str">
         <f t="shared" ref="C28:V28" si="7">IF(C18&gt;C13,"YES","no")</f>
@@ -11309,7 +11405,7 @@
     </row>
     <row r="30" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -11321,7 +11417,7 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B31" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>12</v>
@@ -11341,7 +11437,7 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B32" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C32" s="15">
         <f>SUMIF('Consumer Model'!$C$6:$V$6,1,$C$13:$V$13)</f>
@@ -11491,7 +11587,7 @@
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C38" s="7" t="str">
         <f>IF(C34&gt;C32,"YES","no")</f>
@@ -11516,7 +11612,7 @@
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C39" s="16">
         <f>INDEX('AUM Engine'!$C$68:$V$68,1,4)</f>
@@ -11541,27 +11637,27 @@
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C40" s="16">
-        <f>INDEX('Consumer Model'!$C$19:$V$19,1,4)</f>
-        <v>14764125.523048799</v>
+        <f>INDEX('Consumer Model'!$C$20:$V$20,1,4)</f>
+        <v>18900000</v>
       </c>
       <c r="D40" s="16">
-        <f>INDEX('Consumer Model'!$C$19:$V$19,1,8)</f>
-        <v>64640745.986803554</v>
+        <f>INDEX('Consumer Model'!$C$20:$V$20,1,8)</f>
+        <v>74681250</v>
       </c>
       <c r="E40" s="16">
-        <f>INDEX('Consumer Model'!$C$19:$V$19,1,12)</f>
-        <v>210308962.43938738</v>
+        <f>INDEX('Consumer Model'!$C$20:$V$20,1,12)</f>
+        <v>237750000</v>
       </c>
       <c r="F40" s="16">
-        <f>INDEX('Consumer Model'!$C$19:$V$19,1,16)</f>
-        <v>533532019.70545787</v>
+        <f>INDEX('Consumer Model'!$C$20:$V$20,1,16)</f>
+        <v>594375000</v>
       </c>
       <c r="G40" s="16">
-        <f>INDEX('Consumer Model'!$C$19:$V$19,1,20)</f>
-        <v>1094182806.8164268</v>
+        <f>INDEX('Consumer Model'!$C$20:$V$20,1,20)</f>
+        <v>1188750000</v>
       </c>
     </row>
   </sheetData>
@@ -11582,7 +11678,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11594,12 +11690,12 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -11611,7 +11707,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B5" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C5" s="32">
         <f>Assumptions!$C$5*Assumptions!$C$6</f>
@@ -11620,7 +11716,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B6" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C6" s="32">
         <f>Assumptions!$C$12</f>
@@ -11629,19 +11725,19 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B7" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C7" s="8">
         <f>C5/C6</f>
         <v>1.9200000000000002</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -11673,7 +11769,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B11" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C11" s="16">
         <f>'Revenue Comparison'!C$39</f>
@@ -11698,32 +11794,32 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B12" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C12" s="16">
         <f>'Revenue Comparison'!C$40</f>
-        <v>14764125.523048799</v>
+        <v>18900000</v>
       </c>
       <c r="D12" s="16">
         <f>'Revenue Comparison'!D$40</f>
-        <v>64640745.986803554</v>
+        <v>74681250</v>
       </c>
       <c r="E12" s="16">
         <f>'Revenue Comparison'!E$40</f>
-        <v>210308962.43938738</v>
+        <v>237750000</v>
       </c>
       <c r="F12" s="16">
         <f>'Revenue Comparison'!F$40</f>
-        <v>533532019.70545787</v>
+        <v>594375000</v>
       </c>
       <c r="G12" s="16">
         <f>'Revenue Comparison'!G$40</f>
-        <v>1094182806.8164268</v>
+        <v>1188750000</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B13" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C13" s="8">
         <f>C11/C12</f>
@@ -11731,24 +11827,24 @@
       </c>
       <c r="D13" s="8">
         <f>D11/D12</f>
-        <v>0.23883524132876641</v>
+        <v>0.20672509053383165</v>
       </c>
       <c r="E13" s="8">
         <f>E11/E12</f>
-        <v>0.31141299443525827</v>
+        <v>0.27546979495193219</v>
       </c>
       <c r="F13" s="8">
         <f>F11/F12</f>
-        <v>0.39718542121854367</v>
+        <v>0.35652768030333143</v>
       </c>
       <c r="G13" s="8">
         <f>G11/G12</f>
-        <v>0.43395631898483283</v>
+        <v>0.39943431599793822</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B14" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C14" s="19">
         <f>$C$7</f>
@@ -11773,7 +11869,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B15" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C15" s="11" t="str">
         <f>IF(C13=0,"no AUM yet",C14/C13)</f>
@@ -11781,24 +11877,24 @@
       </c>
       <c r="D15" s="11">
         <f>IF(D13=0,"no AUM yet",D14/D13)</f>
-        <v>8.039014633343168</v>
+        <v>9.2876969846375861</v>
       </c>
       <c r="E15" s="11">
         <f>IF(E13=0,"no AUM yet",E14/E13)</f>
-        <v>6.165445997145639</v>
+        <v>6.9699111669757787</v>
       </c>
       <c r="F15" s="11">
         <f>IF(F13=0,"no AUM yet",F14/F13)</f>
-        <v>4.8340142850901797</v>
+        <v>5.3852761119879293</v>
       </c>
       <c r="G15" s="11">
         <f>IF(G13=0,"no AUM yet",G14/G13)</f>
-        <v>4.4244084392906506</v>
+        <v>4.8067978215720224</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -11810,7 +11906,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B18" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C18" s="40">
         <f>INDEX('AUM Engine'!$C$62:$V$62,1,20)</f>
@@ -11819,7 +11915,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B19" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C19" s="16">
         <f>INDEX('AUM Engine'!$C$70:$V$70,1,20)</f>
@@ -11828,47 +11924,47 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B20" s="7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C20" s="43">
         <f>$C$7*G12/C18</f>
-        <v>17841.452136624539</v>
+        <v>19383.43949044586</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B21" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C21" s="19">
         <f>C20/C19</f>
-        <v>4.4244084392906506</v>
+        <v>4.8067978215720224</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B22" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C22" s="34">
         <v>2142</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B23" s="9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C23" s="34">
         <v>66000</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -11880,27 +11976,27 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B27" s="46" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C27" s="19">
         <f>Assumptions!$C$5*0.1/0.0025</f>
@@ -11925,7 +12021,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B28" s="46" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C28" s="19">
         <f>Assumptions!$C$5*0.1/0.005</f>
@@ -11950,7 +12046,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B29" s="46" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C29" s="19">
         <f>Assumptions!$C$5*0.1/0.0075</f>
@@ -11975,7 +12071,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B30" s="46" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C30" s="19">
         <f>Assumptions!$C$5*0.1/0.01</f>
@@ -12000,17 +12096,17 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -12022,22 +12118,22 @@
     </row>
     <row r="35" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="21" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="21" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="21" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="21" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -12059,7 +12155,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -12072,7 +12168,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="24" x14ac:dyDescent="0.35">
@@ -12092,10 +12188,10 @@
         <v>120</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -12216,7 +12312,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B9" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C9" s="16">
         <f>INDEX('AUM Engine'!$C$20:$V$20,1,20)</f>
@@ -12245,7 +12341,7 @@
     </row>
     <row r="11" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -12287,7 +12383,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B13" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C13" s="18">
         <f>C6*Assumptions!$C$47</f>
@@ -12345,7 +12441,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B15" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C15" s="18">
         <f>C13*Assumptions!$C$49*Assumptions!$C$51-C13*Assumptions!$C$49/Assumptions!$C$53*Assumptions!$C$52</f>
@@ -12403,7 +12499,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B17" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C17" s="18">
         <f>-Assumptions!$C$54</f>
@@ -12432,7 +12528,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B18" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C18" s="47">
         <f>C12+C14+C15+C16+C17</f>
@@ -12461,7 +12557,7 @@
     </row>
     <row r="20" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -12474,7 +12570,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B21" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C21" s="49">
         <f>(1-C7)/(1+Assumptions!$C$58)</f>
@@ -12495,7 +12591,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B22" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C22" s="43">
         <f>C18/(1+Assumptions!$C$58)*(1-C21^Assumptions!$C$59)/(1-C21)</f>
@@ -12524,7 +12620,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B23" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C23" s="8">
         <f>C22/C5</f>
@@ -12553,7 +12649,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B24" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C24" s="51">
         <f>IF(C18&lt;=0,"n/a",C5/C18)</f>
@@ -12611,7 +12707,7 @@
     </row>
     <row r="28" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -12624,27 +12720,27 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B29" s="13" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B30" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C30" s="18">
         <f>(C6*Assumptions!$C$5*0.1/12 + C14 + C15 + C16 + C17)*Assumptions!$E$35 + (D6*Assumptions!$C$5*0.1/12 + D14 + D15 + D16 + D17)*Assumptions!$E$36 + (E6*Assumptions!$C$5*0.1/12 + E14 + E15 + E16 + E17)*Assumptions!$E$37 + (F6*Assumptions!$C$5*0.1/12 + F14 + F15 + F16 + F17)*Assumptions!$E$38</f>
@@ -12669,7 +12765,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -12689,7 +12785,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -12701,12 +12797,12 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -12718,35 +12814,35 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B6" s="13" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B7" s="46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C7" s="19">
         <f>INDEX('AUM Engine'!$C$71:$V$71,1,20)*(0+0.01*36)</f>
@@ -12775,7 +12871,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B8" s="46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C8" s="19">
         <f>INDEX('AUM Engine'!$C$71:$V$71,1,20)*(0+0.02*36)</f>
@@ -12804,7 +12900,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B9" s="46" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C9" s="19">
         <f>INDEX('AUM Engine'!$C$71:$V$71,1,20)*(0+0.03*36)</f>
@@ -12833,7 +12929,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B10" s="46" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C10" s="19">
         <f>INDEX('AUM Engine'!$C$71:$V$71,1,20)*(0+0.05*36)</f>
@@ -12862,7 +12958,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B11" s="46" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C11" s="19">
         <f>INDEX('AUM Engine'!$C$71:$V$71,1,20)*(0+0.08*36)</f>
@@ -12891,7 +12987,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B12" s="7" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C12" s="11">
         <f>'Crossover Analysis'!$C$7</f>
@@ -12900,12 +12996,12 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -12920,24 +13016,24 @@
         <v>19</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B18" s="9" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C18" s="16">
         <f>'Revenue Comparison'!$G$39*0.0025</f>
@@ -12962,7 +13058,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B19" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C19" s="16">
         <f>'Revenue Comparison'!$G$32</f>
@@ -12987,7 +13083,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B20" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C20" s="10">
         <f>C18/C19</f>
@@ -13012,7 +13108,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
